--- a/Zinc/5. Cluster analysis/Typology Plots/Sites_by_typology.xlsx
+++ b/Zinc/5. Cluster analysis/Typology Plots/Sites_by_typology.xlsx
@@ -6,16 +6,17 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="NP Tribs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P Tribs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PD Tribs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Main Stem" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pooled Water" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-Perennial Tribs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Perennial Tribs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Developed Tribs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Main Stem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -23,13 +24,49 @@
     <t xml:space="preserve">Typology</t>
   </si>
   <si>
+    <t xml:space="preserve">MTN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pooled Water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NBO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTN1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL4.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSL6</t>
+  </si>
+  <si>
     <t xml:space="preserve">MCA3.3</t>
   </si>
   <si>
-    <t xml:space="preserve">NP Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCA3.2</t>
+    <t xml:space="preserve">Non-Perennial Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">MTN4</t>
@@ -38,13 +75,10 @@
     <t xml:space="preserve">NBO3</t>
   </si>
   <si>
-    <t xml:space="preserve">WBK2</t>
-  </si>
-  <si>
     <t xml:space="preserve">EFK13.8</t>
   </si>
   <si>
-    <t xml:space="preserve">P Tribs</t>
+    <t xml:space="preserve">Perennial Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">MCA4</t>
@@ -56,12 +90,6 @@
     <t xml:space="preserve">MCA2</t>
   </si>
   <si>
-    <t xml:space="preserve">MCA3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WBK3</t>
-  </si>
-  <si>
     <t xml:space="preserve">BSL5.1</t>
   </si>
   <si>
@@ -107,21 +135,12 @@
     <t xml:space="preserve">BSL8</t>
   </si>
   <si>
-    <t xml:space="preserve">BSL4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSL4.2</t>
-  </si>
-  <si>
     <t xml:space="preserve">BSL2.2</t>
   </si>
   <si>
     <t xml:space="preserve">WBK1</t>
   </si>
   <si>
-    <t xml:space="preserve">NBO5</t>
-  </si>
-  <si>
     <t xml:space="preserve">BSL3.1</t>
   </si>
   <si>
@@ -131,13 +150,7 @@
     <t xml:space="preserve">NBO2</t>
   </si>
   <si>
-    <t xml:space="preserve">BSL4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTN1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PD Tribs</t>
+    <t xml:space="preserve">Developed Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
@@ -538,6 +551,62 @@
         <v>3</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -559,34 +628,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -594,231 +663,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
         <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>29</v>
-      </c>
-      <c r="B25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -842,138 +687,266 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
         <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -997,162 +970,317 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/Zinc/5. Cluster analysis/Typology Plots/Sites_by_typology.xlsx
+++ b/Zinc/5. Cluster analysis/Typology Plots/Sites_by_typology.xlsx
@@ -6,10 +6,10 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Pooled Water" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Non-Perennial Tribs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Perennial Tribs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Developed Tribs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pooled" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Non-Perennial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Perennial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Developed Perennial" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Main Stem" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
@@ -27,7 +27,7 @@
     <t xml:space="preserve">MTN2</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled Water</t>
+    <t xml:space="preserve">Pooled</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.1</t>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">MCA3.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
+    <t xml:space="preserve">Non-Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">MTN4</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">EFK13.8</t>
   </si>
   <si>
-    <t xml:space="preserve">Perennial Tribs</t>
+    <t xml:space="preserve">Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">MCA4</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">NBO2</t>
   </si>
   <si>
-    <t xml:space="preserve">Developed Tribs</t>
+    <t xml:space="preserve">Developed Perennial</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
